--- a/data/ИПП.xlsx
+++ b/data/ИПП.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vasil\YandexDisk\project\LK_and_commets\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83260DB3-CF21-4EC0-955E-A2FD4834ACF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D70F25A-EC4C-4F72-A85A-722702F04086}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="4230" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -519,7 +519,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:EO5"/>
+  <dimension ref="A1:EP5"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="52.08984375" customWidth="1"/>
@@ -554,7 +554,7 @@
     <col min="143" max="144" width="9" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:145" s="1" customFormat="1" ht="14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:146" s="1" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -562,7 +562,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:145" s="1" customFormat="1" ht="45" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:146" s="1" customFormat="1" ht="45" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
@@ -998,8 +998,11 @@
       <c r="EO2" s="3">
         <v>46023</v>
       </c>
+      <c r="EP2" s="3">
+        <v>46054</v>
+      </c>
     </row>
-    <row r="3" spans="1:145" s="1" customFormat="1" ht="28" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:146" s="1" customFormat="1" ht="28" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>3</v>
       </c>
@@ -1446,8 +1449,11 @@
       <c r="EO3" s="9">
         <v>76.3</v>
       </c>
+      <c r="EP3" s="1">
+        <v>98.8</v>
+      </c>
     </row>
-    <row r="4" spans="1:145" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:146" s="1" customFormat="1" ht="28.5" x14ac:dyDescent="0.35">
       <c r="A4" s="5" t="s">
         <v>4</v>
       </c>
@@ -1847,8 +1853,11 @@
       <c r="EO4" s="9">
         <v>99.2</v>
       </c>
+      <c r="EP4" s="1">
+        <v>99.1</v>
+      </c>
     </row>
-    <row r="5" spans="1:145" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:146" ht="15.5" x14ac:dyDescent="0.35">
       <c r="M5" s="8"/>
       <c r="N5" s="8"/>
       <c r="O5" s="8"/>
